--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-body-height.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-body-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T10:38:49+00:00</t>
+    <t>2025-02-11T11:03:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-body-height.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-body-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:03:37+00:00</t>
+    <t>2025-02-11T12:08:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -660,7 +660,8 @@
     <t>FR Core Observation Height Body Position Extension</t>
   </si>
   <si>
-    <t>Extension on the FrObservationBodyHeight to specify the position of the body during the measure of the height. | Extension utilisée par le profil FrObservationBodyHeight permettant de préciser la position du corps durant la mesure de la taille (le jeu de valeur associé est limité aux 2 valeurs lying et standing)</t>
+    <t>Extension utilisée par le profil FrObservationBodyHeight permettant de préciser la position du corps durant la mesure de la taille (le jeu de valeur associé est limité aux 2 valeurs lying et standing).
+Extension on the FrObservationBodyHeight to specify the position of the body during the measure of the height.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-body-height.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-body-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:08:53+00:00</t>
+    <t>2025-02-11T15:31:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-body-height.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-body-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:31:42+00:00</t>
+    <t>2025-02-11T17:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-body-height.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-body-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:07:06+00:00</t>
+    <t>2025-02-11T17:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-body-height.xlsx
+++ b/nr-uniformisation-descriptions/ig/StructureDefinition-fr-core-observation-body-height.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T17:08:15+00:00</t>
+    <t>2025-02-11T17:29:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
